--- a/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dounia va à la boulangerie. Elle marche avec maman. Elles arrivent au bord. Dounia donne la main. La main est dans la main. Maman est l'adulte. Elles restent sur le trottoir. Elles restent sur le trottoir en attendant. Dounia attend. Elle sent la main de maman. Maman dit : on attend le feu vert. Dounia regarde maman. Le feu est vert. Maman dit : feu vert. On avance avec l'adulte. Dounia tient la main. Elles marchent ensemble. La main reste tenue. L'adulte est là. Ça sent le pain chaud. Dounia dit : merci maman.</t>
+          <t>Dounia va à la boulangerie. Elle marche avec maman. Elles arrivent au bord. Dounia donne la main. La main est dans la main. Maman est l'adulte. Elles restent sur le trottoir. Elles restent sur le trottoir en attendant. Dounia attend. Elle sent la main de maman. On attend le feu vert. Dounia regarde maman. Le feu est vert. Feu vert. On avance avec l'adulte. Dounia tient la main. Elles marchent ensemble. La main reste tenue. L'adulte est là. Ça sent le pain chaud. Merci maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia va à la boulangerie. Elle marche avec maman. Elles arrivent au bord. Dounia donne la main. La main est dans la main. Maman est l'adulte. Elles restent sur le trottoir. Elles restent sur le trottoir en attendant. Dounia attend. Elle sent la main de maman.
+maman|On attend le feu vert.
+narrateur|Dounia regarde maman. Le feu est vert.
+maman|Feu vert. On avance avec l'adulte.
+narrateur|Dounia tient la main. Elles marchent ensemble. La main reste tenue. L'adulte est là. Ça sent le pain chaud.
+enfant-f|Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia attend avec maman. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia a donné la main. Elle a attendu le feu vert. Maman était là. Les pieds étaient sur le trottoir en attendant.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1843,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia serre la main de maman. Elles tiennent la baguette.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2010,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2050,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 enfant-f|Merci maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Dounia attend avec maman. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Dounia a donné la main. Elle a attendu le feu vert. Maman était là. Les pieds étaient sur le trottoir en attendant.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1848,6 +1856,7 @@
           <t>narrateur|Dounia serre la main de maman. Elles tiennent la baguette.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2015,6 +2024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2067,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dounia attend le feu vert</t>
+          <t>Le goéland du port</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un goéland crie. Mila veut la galette du port. Le ruban vole vers la bordure. Elle serre la main, attend le vert. Le sel reste sur les lèvres.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dounia va à la boulangerie. Elle marche avec maman. Elles arrivent au bord. Dounia donne la main. La main est dans la main. Maman est l'adulte. Elles restent sur le trottoir. Elles restent sur le trottoir en attendant. Dounia attend. Elle sent la main de maman. On attend le feu vert. Dounia regarde maman. Le feu est vert. Feu vert. On avance avec l'adulte. Dounia tient la main. Elles marchent ensemble. La main reste tenue. L'adulte est là. Ça sent le pain chaud. Merci maman.</t>
+          <t>Un goéland crie au-dessus des mâts. Les mâts sont minces, tout loin. L'air sent le sel et le pain. Une corde frappe un mât, toc toc. L'eau clignote, toute plate. Mila vit ici, près du port. Son manteau sent encore le vent. Maman, le goéland ! Oui. Il a un bec jaune. On va chercher la galette ? Oui, maman. En ce moment, Mila prend le ruban. Le ruban bleu vole un peu. Tu mets ton bonnet ? Il chatouille. Il te tient chaud. Maman tend la main. Je prends ta main. Merci, Mila. Elles marchent sur le trottoir du quai. Les dalles sont froides et râpeuses. Un bateau cliquette, tout loin. J'entends l'eau. On reste sur le trottoir. La boulangerie du port est plus loin. La galette est chaude ? Oui. Bientôt. Le bord du quai arrive, tout blanc. Une chaîne froide marque la bordure. Le vent pousse le ruban bleu. Le ruban vole vers la bordure. Mon ruban ! On reste sur le trottoir. Tu serres ma main ? Mila serre la main. Ses pieds restent sur le trottoir. Le ruban s'accroche à la chaîne. Le petit bonhomme est encore rouge. On attend le vert. Mila regarde le feu piéton. Le goéland glisse, tout blanc. Une voiture passe tout doucement. Il crie encore. On attend ensemble. Le pain du port sent, tout près. Mila sent le beurre dans l'air. Ses doigts restent dans la main. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Elles marchent, main dans la main. La clochette de la porte tinte. La galette est ronde et dorée. Elle est chaude ! Tu la tiens ? Mila tient la galette tiède.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dounia va à la boulangerie. Elle marche avec maman. Elles arrivent au bord. Dounia donne la main. La main est dans la main. Maman est l'adulte. Elles restent sur le trottoir. Elles restent sur le trottoir en attendant. Dounia attend. Elle sent la main de maman. Maman dit : on attend le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Dounia regarde maman. Le feu est vert. Maman dit : feu vert. On avance avec l'adulte. Dounia tient la main. Elles marchent ensemble. La main reste tenue. L'adulte est là. Ça sent le pain chaud. Dounia dit : merci maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un goéland crie au-dessus des mâts. Les mâts sont minces, tout loin. L'air sent le sel et le pain. Une corde frappe un mât, toc toc. L'eau clignote, toute plate. Mila vit ici, près du port. Son manteau sent encore le vent. Maman, le goéland ! Oui. Il a un bec jaune. On va chercher la galette ? Oui, maman. En ce moment, Mila prend le ruban. Le ruban bleu vole un peu. Tu mets ton bonnet ? Il chatouille. Il te tient chaud. Maman tend la main. Je prends ta main. Merci, Mila. Elles marchent sur le trottoir du quai. Les dalles sont froides et râpeuses. Un bateau cliquette, tout loin. J'entends l'eau. On reste sur le trottoir. La boulangerie du port est plus loin. La galette est chaude ? Oui. Bientôt. Le bord du quai arrive, tout blanc. Une chaîne froide marque la bordure. Le vent pousse le ruban bleu. Le ruban vole vers la bordure. Mon ruban ! On reste sur le trottoir. Tu serres ma main ? Mila serre la main. Ses pieds restent sur le trottoir. Le ruban s'accroche à la chaîne. Le petit bonhomme est encore rouge. On attend le vert. Mila regarde le feu piéton. Le goéland glisse, tout blanc. Une voiture passe tout doucement. Il crie encore. On attend ensemble. Le pain du port sent, tout près. Mila sent le beurre dans l'air. Ses doigts restent dans la main. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Elles marchent, main dans la main. La clochette de la porte tinte. La galette est ronde et dorée. Elle est chaude ! Tu la tiens ? Mila tient la galette tiède.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dounia va à la boulangerie. Elle marche avec maman. Elles arrivent au bord. Dounia donne la main. La main est dans la main. Maman est l'adulte. Elles restent sur le trottoir. Elles restent sur le trottoir en attendant. Dounia attend. Elle sent la main de maman.
-maman|On attend le feu vert.
-narrateur|Dounia regarde maman. Le feu est vert.
-maman|Feu vert. On avance avec l'adulte.
-narrateur|Dounia tient la main. Elles marchent ensemble. La main reste tenue. L'adulte est là. Ça sent le pain chaud.
-enfant-f|Merci maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un goéland crie au-dessus des mâts.
+narrateur|Les mâts sont minces, tout loin.
+narrateur|L'air sent le sel et le pain.
+narrateur|Une corde frappe un mât, toc toc.
+narrateur|L'eau clignote, toute plate.
+narrateur|Mila vit ici, près du port.
+narrateur|Son manteau sent encore le vent.
+enfant-f|Maman, le goéland !
+maman|Oui.
+maman|Il a un bec jaune.
+maman|On va chercher la galette ?
+enfant-f|Oui, maman.
+narrateur|En ce moment, Mila prend le ruban.
+narrateur|Le ruban bleu vole un peu.
+maman|Tu mets ton bonnet ?
+enfant-f|Il chatouille.
+maman|Il te tient chaud.
+narrateur|Maman tend la main.
+enfant-f|Je prends ta main.
+maman|Merci, Mila.
+narrateur|Elles marchent sur le trottoir du quai.
+narrateur|Les dalles sont froides et râpeuses.
+narrateur|Un bateau cliquette, tout loin.
+enfant-f|J'entends l'eau.
+maman|On reste sur le trottoir.
+narrateur|La boulangerie du port est plus loin.
+enfant-f|La galette est chaude ?
+maman|Oui.
+maman|Bientôt.
+narrateur|Le bord du quai arrive, tout blanc.
+narrateur|Une chaîne froide marque la bordure.
+narrateur|Le vent pousse le ruban bleu.
+narrateur|Le ruban vole vers la bordure.
+enfant-f|Mon ruban !
+maman|On reste sur le trottoir.
+maman|Tu serres ma main ?
+narrateur|Mila serre la main.
+narrateur|Ses pieds restent sur le trottoir.
+narrateur|Le ruban s'accroche à la chaîne.
+narrateur|Le petit bonhomme est encore rouge.
+maman|On attend le vert.
+narrateur|Mila regarde le feu piéton.
+narrateur|Le goéland glisse, tout blanc.
+narrateur|Une voiture passe tout doucement.
+enfant-f|Il crie encore.
+maman|On attend ensemble.
+narrateur|Le pain du port sent, tout près.
+narrateur|Mila sent le beurre dans l'air.
+narrateur|Ses doigts restent dans la main.
+narrateur|Puis le petit bonhomme devient vert.
+maman|Feu vert.
+maman|On avance ensemble.
+narrateur|Elles marchent, main dans la main.
+narrateur|La clochette de la porte tinte.
+narrateur|La galette est ronde et dorée.
+enfant-f|Elle est chaude !
+maman|Tu la tiens ?
+narrateur|Mila tient la galette tiède.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1413,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dounia attend avec maman. Que fait-elle ?</t>
+          <t>Mila attend avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dounia attend avec maman. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila attend avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1433,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>feu vert | la main | avec maman | avec l'adulte | attendre</t>
+          <t>feu vert | la main | avec maman | avec papa | avec l'adulte | attendre | le vert</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1448,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle donne la main. Elle attend le feu vert. Que fait Dounia ?</t>
+          <t>Elle serre la main. Elle attend le feu vert. Que fait Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1497,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1573,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Dounia attend avec maman. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila attend avec maman.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dounia a donné la main. Elle a attendu le feu vert. Maman était là. Les pieds étaient sur le trottoir en attendant.</t>
+          <t>Mila a serré la main. Elle a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, maman. Le ruban bleu dort sur la chaîne. La galette chauffe les paumes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dounia a donné la main. Elle a attendu le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Maman était là. Les pieds étaient sur le trottoir en attendant.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a serré la main. Elle a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, maman. Le ruban bleu dort sur la chaîne. La galette chauffe les paumes.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,14 +1662,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1749,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dounia a donné la main. Elle a attendu le feu vert. Maman était là. Les pieds étaient sur le trottoir en attendant.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a serré la main.
+narrateur|Elle a attendu le feu vert.
+narrateur|Ses pieds restaient sur le trottoir.
+maman|Tu as attendu le vert ?
+enfant-f|Oui, maman.
+narrateur|Le ruban bleu dort sur la chaîne.
+narrateur|La galette chauffe les paumes.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dounia serre la main de maman. Elles tiennent la baguette.</t>
+          <t>Elles s'assoient sur le banc du quai. Mila souffle sur la galette. Le beurre brille un peu. Ça sent le sel. Oui. Tu mords un bout ? Un bout craque, tout doux. Des miettes tombent sur le manteau. Le goéland les regarde, puis part. Il s'envole. On ramasse le ruban ? Sur le trottoir. Maman décroche le ruban, tout près. Le vent sent encore le large.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dounia serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Elles tiennent la baguette.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles s'assoient sur le banc du quai. Mila souffle sur la galette. Le beurre brille un peu. Ça sent le sel. Oui. Tu mords un bout ? Un bout craque, tout doux. Des miettes tombent sur le manteau. Le goéland les regarde, puis part. Il s'envole. On ramasse le ruban ? Sur le trottoir. Maman décroche le ruban, tout près. Le vent sent encore le large.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,14 +1843,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1853,10 +1926,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Dounia serre la main de maman. Elles tiennent la baguette.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles s'assoient sur le banc du quai.
+narrateur|Mila souffle sur la galette.
+narrateur|Le beurre brille un peu.
+enfant-f|Ça sent le sel.
+maman|Oui.
+maman|Tu mords un bout ?
+narrateur|Un bout craque, tout doux.
+narrateur|Des miettes tombent sur le manteau.
+narrateur|Le goéland les regarde, puis part.
+enfant-f|Il s'envole.
+maman|On ramasse le ruban ?
+enfant-f|Sur le trottoir.
+narrateur|Maman décroche le ruban, tout près.
+narrateur|Le vent sent encore le large.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1881,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila lèche une miette salée. Les mâts bougent un tout petit peu. La galette est à nous. Oui. Le goéland glisse au-dessus des mâts.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila lèche une miette salée. Les mâts bougent un tout petit peu. La galette est à nous. Oui. Le goéland glisse au-dessus des mâts.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,14 +2027,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2021,10 +2106,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Mila lèche une miette salée.
+narrateur|Les mâts bougent un tout petit peu.
+enfant-f|La galette est à nous.
+maman|Oui.
+narrateur|Le goéland glisse au-dessus des mâts.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2043,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,6 +2169,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers la boulangerie</t>
+          <t>quai du port, mâts au loin, boulangerie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dounia, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
